--- a/django/camac/statistics/config/kt_ag/work-items_service-cantonal.xlsx
+++ b/django/camac/statistics/config/kt_ag/work-items_service-cantonal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA40778-0D49-44B3-80D4-457AA586DC46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B853E9D9-2AC3-4FBB-ADC8-7A228D847A6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="31755" windowHeight="16770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="20565" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -18,13 +18,13 @@
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="67" r:id="rId3"/>
+    <pivotCache cacheId="35" r:id="rId3"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Dossier-Nr.</t>
   </si>
@@ -71,22 +71,19 @@
     <t>Fristgerecht</t>
   </si>
   <si>
-    <t>Zeilenbeschriftungen</t>
-  </si>
-  <si>
     <t>Anzahl</t>
   </si>
   <si>
     <t>Anteil</t>
   </si>
   <si>
-    <t>(Leer)</t>
-  </si>
-  <si>
     <t>Gesamtergebnis</t>
   </si>
   <si>
-    <t>Nicht fristgerecht</t>
+    <t>Frist erreicht</t>
+  </si>
+  <si>
+    <t>Anzahl fristgerechter Dossiers</t>
   </si>
 </sst>
 </file>
@@ -155,13 +152,13 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Stoppe Tilo  Extern" refreshedDate="46111.704483333335" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="18" xr:uid="{702360AB-C9CD-44A0-83E7-D79DA84FAFC7}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Stoppe Tilo  Extern" refreshedDate="46121.734099884263" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="43" xr:uid="{702360AB-C9CD-44A0-83E7-D79DA84FAFC7}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:O1048576" sheet="Data"/>
   </cacheSource>
   <cacheFields count="15">
     <cacheField name="Dossier-Nr." numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="17"/>
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name="Gesuchstyp" numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
@@ -203,10 +200,10 @@
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name="Fristgerecht" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="1" count="3">
-        <n v="1"/>
-        <n v="0"/>
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="1" count="3">
         <m/>
+        <n v="1" u="1"/>
+        <n v="0" u="1"/>
       </sharedItems>
     </cacheField>
   </cacheFields>
@@ -219,319 +216,744 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="18">
-  <r>
-    <n v="1"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="2"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="3"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="4"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="5"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="6"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="7"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="8"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="9"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="10"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="11"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="12"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="13"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="14"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="15"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="16"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="17"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="43">
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3A66BD08-8A2A-4630-9E47-62102FFF2B2D}" name="PivotTable8" cacheId="67" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:C7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3A66BD08-8A2A-4630-9E47-62102FFF2B2D}" name="PivotTable8" cacheId="35" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Frist erreicht">
+  <location ref="A3:C4" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
@@ -549,9 +971,9 @@
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="4">
-        <item n="Nicht fristgerecht" x="1"/>
-        <item n="Fristgerecht" x="0"/>
-        <item x="2"/>
+        <item h="1" x="0"/>
+        <item n="Fristgerecht" m="1" x="1"/>
+        <item n="nicht Fristgerecht" m="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -559,16 +981,7 @@
   <rowFields count="1">
     <field x="14"/>
   </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
+  <rowItems count="1">
     <i t="grand">
       <x/>
     </i>
@@ -991,65 +1404,37 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F77C9CE-FA2F-4825-8723-073E40AAD081}">
-  <dimension ref="A3:C7"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+    </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="5">
-        <v>9</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0.52941176470588236</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="5">
-        <v>8</v>
-      </c>
-      <c r="C5" s="3">
-        <v>0.47058823529411764</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="5">
         <v>17</v>
       </c>
-      <c r="C7" s="3">
-        <v>1</v>
+      <c r="B4" s="5"/>
+      <c r="C4" s="3" t="e">
+        <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
@@ -1058,6 +1443,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e238f3b-cf1c-4dc8-b1c3-14677632393c">
@@ -1066,15 +1460,6 @@
     <TaxCatchAll xmlns="fb274a4b-4ecf-4ae2-a446-66548455045d" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1318,20 +1703,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66DE17A2-A0EB-48D3-A057-CDAE41D7929E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89DA5A24-00D7-46D1-A57E-9371D8E3F520}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="5e238f3b-cf1c-4dc8-b1c3-14677632393c"/>
     <ds:schemaRef ds:uri="fb274a4b-4ecf-4ae2-a446-66548455045d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66DE17A2-A0EB-48D3-A057-CDAE41D7929E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/django/camac/statistics/config/kt_ag/work-items_service-cantonal.xlsx
+++ b/django/camac/statistics/config/kt_ag/work-items_service-cantonal.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B853E9D9-2AC3-4FBB-ADC8-7A228D847A6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE309D5-7F17-4D90-8510-72027B02B9B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="20565" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2640" yWindow="2640" windowWidth="28800" windowHeight="14925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="35" r:id="rId3"/>
+    <pivotCache cacheId="67" r:id="rId3"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -90,7 +90,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -103,6 +106,13 @@
       <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -125,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -133,6 +143,8 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -152,7 +164,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Stoppe Tilo  Extern" refreshedDate="46121.734099884263" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="43" xr:uid="{702360AB-C9CD-44A0-83E7-D79DA84FAFC7}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Stoppe Tilo  Extern" refreshedDate="46136.440803587961" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="10" xr:uid="{702360AB-C9CD-44A0-83E7-D79DA84FAFC7}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:O1048576" sheet="Data"/>
   </cacheSource>
@@ -202,8 +214,8 @@
     <cacheField name="Fristgerecht" numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="1" count="3">
         <m/>
+        <n v="0" u="1"/>
         <n v="1" u="1"/>
-        <n v="0" u="1"/>
       </sharedItems>
     </cacheField>
   </cacheFields>
@@ -216,7 +228,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="43">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="10">
   <r>
     <m/>
     <m/>
@@ -387,573 +399,12 @@
     <m/>
     <x v="0"/>
   </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3A66BD08-8A2A-4630-9E47-62102FFF2B2D}" name="PivotTable8" cacheId="35" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Frist erreicht">
-  <location ref="A3:C4" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3A66BD08-8A2A-4630-9E47-62102FFF2B2D}" name="PivotTable8" cacheId="67" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Frist erreicht">
+  <location ref="A5:C6" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
@@ -972,8 +423,8 @@
     <pivotField axis="axisRow" showAll="0">
       <items count="4">
         <item h="1" x="0"/>
-        <item n="Fristgerecht" m="1" x="1"/>
-        <item n="nicht Fristgerecht" m="1" x="2"/>
+        <item n="Fristgerecht" m="1" x="2"/>
+        <item n="nicht Fristgerecht" m="1" x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -1330,7 +781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -1397,6 +848,60 @@
         <v>14</v>
       </c>
     </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1404,7 +909,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F77C9CE-FA2F-4825-8723-073E40AAD081}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
@@ -1412,28 +917,28 @@
     <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="3" t="e">
+      <c r="B6" s="7"/>
+      <c r="C6" s="3" t="e">
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -1443,26 +948,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e238f3b-cf1c-4dc8-b1c3-14677632393c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb274a4b-4ecf-4ae2-a446-66548455045d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100D7FFFCF5F95BC94D9B7DF34B9D0CF76C" ma:contentTypeVersion="15" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="a8184ac6384f947bbc55bc4d9e1749d1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5e238f3b-cf1c-4dc8-b1c3-14677632393c" xmlns:ns3="a7360a35-2516-4210-888a-7cc8dd0a384d" xmlns:ns4="fb274a4b-4ecf-4ae2-a446-66548455045d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6dc33f40212c2dffa236803017f7661f" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="5e238f3b-cf1c-4dc8-b1c3-14677632393c"/>
@@ -1702,26 +1187,27 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e238f3b-cf1c-4dc8-b1c3-14677632393c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb274a4b-4ecf-4ae2-a446-66548455045d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66DE17A2-A0EB-48D3-A057-CDAE41D7929E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89DA5A24-00D7-46D1-A57E-9371D8E3F520}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="5e238f3b-cf1c-4dc8-b1c3-14677632393c"/>
-    <ds:schemaRef ds:uri="fb274a4b-4ecf-4ae2-a446-66548455045d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F8560DD-B8D0-49E2-9D3A-1005545CC2EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1739,4 +1225,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66DE17A2-A0EB-48D3-A057-CDAE41D7929E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89DA5A24-00D7-46D1-A57E-9371D8E3F520}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5e238f3b-cf1c-4dc8-b1c3-14677632393c"/>
+    <ds:schemaRef ds:uri="fb274a4b-4ecf-4ae2-a446-66548455045d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/django/camac/statistics/config/kt_ag/work-items_service-cantonal.xlsx
+++ b/django/camac/statistics/config/kt_ag/work-items_service-cantonal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE309D5-7F17-4D90-8510-72027B02B9B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D6BD578-8097-41CE-91E4-58AD90EF35DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="2640" windowWidth="28800" windowHeight="14925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="33105" windowHeight="17610" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -18,13 +18,13 @@
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="67" r:id="rId3"/>
+    <pivotCache cacheId="20" r:id="rId3"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Dossier-Nr.</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>Anzahl fristgerechter Dossiers</t>
+  </si>
+  <si>
+    <t>Fristgerecht: 0 = nicht fristgerecht, 1 = fristgerecht</t>
   </si>
 </sst>
 </file>
@@ -93,7 +96,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -109,6 +112,14 @@
     </font>
     <font>
       <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -135,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -146,6 +157,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -164,7 +176,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Stoppe Tilo  Extern" refreshedDate="46136.440803587961" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="10" xr:uid="{702360AB-C9CD-44A0-83E7-D79DA84FAFC7}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Stoppe Tilo  Extern" refreshedDate="46146.647656712965" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="10" xr:uid="{702360AB-C9CD-44A0-83E7-D79DA84FAFC7}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:O1048576" sheet="Data"/>
   </cacheSource>
@@ -403,7 +415,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3A66BD08-8A2A-4630-9E47-62102FFF2B2D}" name="PivotTable8" cacheId="67" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Frist erreicht">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3A66BD08-8A2A-4630-9E47-62102FFF2B2D}" name="PivotTable8" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Frist erreicht">
   <location ref="A5:C6" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField dataField="1" showAll="0"/>
@@ -909,7 +921,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F77C9CE-FA2F-4825-8723-073E40AAD081}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
@@ -917,12 +929,15 @@
     <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>19</v>
       </c>
+      <c r="H1" s="8" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
@@ -933,7 +948,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -948,6 +963,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e238f3b-cf1c-4dc8-b1c3-14677632393c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb274a4b-4ecf-4ae2-a446-66548455045d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100D7FFFCF5F95BC94D9B7DF34B9D0CF76C" ma:contentTypeVersion="15" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="a8184ac6384f947bbc55bc4d9e1749d1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5e238f3b-cf1c-4dc8-b1c3-14677632393c" xmlns:ns3="a7360a35-2516-4210-888a-7cc8dd0a384d" xmlns:ns4="fb274a4b-4ecf-4ae2-a446-66548455045d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6dc33f40212c2dffa236803017f7661f" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="5e238f3b-cf1c-4dc8-b1c3-14677632393c"/>
@@ -1187,27 +1222,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e238f3b-cf1c-4dc8-b1c3-14677632393c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb274a4b-4ecf-4ae2-a446-66548455045d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89DA5A24-00D7-46D1-A57E-9371D8E3F520}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5e238f3b-cf1c-4dc8-b1c3-14677632393c"/>
+    <ds:schemaRef ds:uri="fb274a4b-4ecf-4ae2-a446-66548455045d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66DE17A2-A0EB-48D3-A057-CDAE41D7929E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F8560DD-B8D0-49E2-9D3A-1005545CC2EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1225,23 +1259,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66DE17A2-A0EB-48D3-A057-CDAE41D7929E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89DA5A24-00D7-46D1-A57E-9371D8E3F520}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="5e238f3b-cf1c-4dc8-b1c3-14677632393c"/>
-    <ds:schemaRef ds:uri="fb274a4b-4ecf-4ae2-a446-66548455045d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>